--- a/ig/DM-JANVIER-2025/ValueSet-1.2.250.1.213.1.1.5.708.xlsx
+++ b/ig/DM-JANVIER-2025/ValueSet-1.2.250.1.213.1.1.5.708.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
   <si>
     <t>Property</t>
   </si>
@@ -36,13 +36,13 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20241126000000</t>
+    <t>20231121000000</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>JDV_Rencontre_CS8_CISIS</t>
+    <t>JDV_Rencontre_CSE_CISIS</t>
   </si>
   <si>
     <t>Title</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>retired</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-26T00:00:00+01:00</t>
+    <t>2023-11-21T00:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,22 +90,19 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>ORG-196</t>
+    <t>ORG-083</t>
+  </si>
+  <si>
+    <t>Demande de rappel par le médecin de PMI</t>
   </si>
   <si>
     <t>Lien avec le médecin de PMI après accord des parents</t>
   </si>
   <si>
-    <t>ORG-194</t>
-  </si>
-  <si>
-    <t>Orientation vers un autre professionnel de santé</t>
-  </si>
-  <si>
-    <t>ORG-195</t>
-  </si>
-  <si>
-    <t>Orientation vers une structure pluridisciplinaire (CAMPS centre de référence, réseau…)</t>
+    <t>ORG-084</t>
+  </si>
+  <si>
+    <t>Demande de consultation médicale spécialisée</t>
   </si>
   <si>
     <t/>
@@ -370,7 +367,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -395,34 +392,42 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>27</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
